--- a/i18n/pl.xlsx
+++ b/i18n/pl.xlsx
@@ -9,7 +9,7 @@
     </mc:Choice>
   </mc:AlternateContent>
   <bookViews>
-    <workbookView xWindow="0" yWindow="0" windowWidth="16380" windowHeight="8190" tabRatio="500"/>
+    <workbookView xWindow="0" yWindow="0" windowWidth="16380" windowHeight="8190" tabRatio="500" activeTab="2"/>
   </bookViews>
   <sheets>
     <sheet name="Birds" sheetId="1" r:id="rId1"/>
@@ -4320,6 +4320,7 @@
         <sz val="12"/>
         <color rgb="FF000000"/>
         <rFont val="Calibri"/>
+        <family val="2"/>
         <charset val="238"/>
       </rPr>
       <t>–</t>
@@ -5427,6 +5428,7 @@
         <sz val="10"/>
         <color rgb="FF000000"/>
         <rFont val="Calibri"/>
+        <family val="2"/>
         <charset val="238"/>
       </rPr>
       <t>Za zgodą wydawcy wersji angielskiej zadania w tej kategorii zostały zmodyfikowane.&lt;br&gt;Policz zagrane karty ptaków, które w swojej nazwie mają jedno z poniższych określeń. Części ciała mogą być różnie odmienione lub stanowić część innego wyrazu, np. żółtoczelny, płaskonos.&lt;br&gt;</t>
@@ -5436,7 +5438,8 @@
         <sz val="10"/>
         <color rgb="FF000000"/>
         <rFont val="Calibri"/>
-        <charset val="1"/>
+        <family val="2"/>
+        <charset val="238"/>
       </rPr>
       <t>Podczas gry z dodatkiem Ptaki Europy, Ptaki Oceanii lub Ptaki Azji ze względu na zmienioną wartość procentową nie zaleca się korzystania z tej karty bonusowej.</t>
     </r>
@@ -5546,6 +5549,7 @@
         <sz val="10"/>
         <color rgb="FF000000"/>
         <rFont val="Calibri"/>
+        <family val="2"/>
         <charset val="238"/>
       </rPr>
       <t>Za zgodą wydawcy wersji angielskiej zadania w tej kategorii zostały zmodyfikowane.&lt;br&gt;Policz zagrane karty ptaków, które w swojej nazwie mają jedno z poniższych określeń.&lt;br&gt;</t>
@@ -5555,7 +5559,8 @@
         <sz val="10"/>
         <color rgb="FF000000"/>
         <rFont val="Calibri"/>
-        <charset val="1"/>
+        <family val="2"/>
+        <charset val="238"/>
       </rPr>
       <t>Podczas gry z dodatkiem Ptaki Europy, Ptaki Oceanii lub Ptaki Azji ze względu na zmienioną wartość procentową nie zaleca się korzystania z tej karty bonusowej.</t>
     </r>
@@ -5617,7 +5622,8 @@
         <sz val="10"/>
         <color rgb="FF000000"/>
         <rFont val="Arial"/>
-        <charset val="1"/>
+        <family val="2"/>
+        <charset val="238"/>
       </rPr>
       <t>Policz liczbę zagranych kart ptaków z określonym symbolem typu gniazda.</t>
     </r>
@@ -5626,6 +5632,7 @@
         <sz val="10"/>
         <color rgb="FF000000"/>
         <rFont val="Calibri"/>
+        <family val="2"/>
         <charset val="238"/>
       </rPr>
       <t>&lt;br&gt;</t>
@@ -5635,7 +5642,8 @@
         <sz val="10"/>
         <color rgb="FF000000"/>
         <rFont val="Arial"/>
-        <charset val="1"/>
+        <family val="2"/>
+        <charset val="238"/>
       </rPr>
       <t>Symbol [star] oznacza gniazdo pasujące do wszystkich 4 bonusów związanych z gniazdami.</t>
     </r>
@@ -5790,6 +5798,7 @@
         <sz val="10"/>
         <color rgb="FF000000"/>
         <rFont val="Calibri"/>
+        <family val="2"/>
         <charset val="238"/>
       </rPr>
       <t>Za zgodą wydawcy wersji angielskiej zadania w tej kategorii zostały zmodyfikowane.&lt;br&gt;</t>
@@ -5799,7 +5808,8 @@
         <sz val="10"/>
         <color rgb="FF000000"/>
         <rFont val="Calibri"/>
-        <charset val="1"/>
+        <family val="2"/>
+        <charset val="238"/>
       </rPr>
       <t>Policz zagrane karty ptaków, które w swojej nazwie mają jedno z poniższych określeń. Kolory mogą być różnie odmienione lub stanowić część innego wyrazu, np. różowogłowy, bursztynka. Każdy ptak liczy się raz, nawet jeśli w swej nazwie ma więcej niż 1 kolor.</t>
     </r>
@@ -5808,6 +5818,7 @@
         <sz val="10"/>
         <color rgb="FF000000"/>
         <rFont val="Calibri"/>
+        <family val="2"/>
         <charset val="238"/>
       </rPr>
       <t>&lt;br&gt;</t>
@@ -5817,7 +5828,8 @@
         <sz val="10"/>
         <color rgb="FF000000"/>
         <rFont val="Calibri"/>
-        <charset val="1"/>
+        <family val="2"/>
+        <charset val="238"/>
       </rPr>
       <t>Podczas gry z dodatkiem Ptaki Europy, Ptaki Oceanii lub Ptaki Azji ze względu na zmienioną wartość procentową nie zaleca się korzystania z tej karty bonusowej. Kolor pstry uznawany jest wyłącznie w dodatku Ptaki Azji.</t>
     </r>
@@ -6079,6 +6091,7 @@
         <sz val="12"/>
         <color rgb="FF000000"/>
         <rFont val="Calibri"/>
+        <family val="2"/>
         <charset val="238"/>
       </rPr>
       <t>].</t>
@@ -6127,6 +6140,7 @@
         <sz val="12"/>
         <color rgb="FF000000"/>
         <rFont val="Calibri"/>
+        <family val="2"/>
         <charset val="238"/>
       </rPr>
       <t>grassland].</t>
@@ -6193,6 +6207,7 @@
         <sz val="12"/>
         <color rgb="FF000000"/>
         <rFont val="Calibri"/>
+        <family val="2"/>
         <charset val="238"/>
       </rPr>
       <t>].</t>
@@ -6250,123 +6265,72 @@
     <t>Explanatory Text</t>
   </si>
   <si>
-    <t>Bird in Forest</t>
-  </si>
-  <si>
     <t>[bird] w [forest]</t>
   </si>
   <si>
     <t>Policz liczbę ptaków, jakie aktualnie masz &lt;b&gt;w tym konkretnym rzędzie.&lt;/b&gt;&lt;br&gt;&lt;i&gt;Istnieje 1 kopia tego celu dla każdego siedliska.&lt;/i&gt;</t>
   </si>
   <si>
-    <t>Bird in Grassland</t>
-  </si>
-  <si>
     <t>[bird] w [grassland]</t>
   </si>
   <si>
-    <t>Bird in Wetland</t>
-  </si>
-  <si>
     <t>[bird] w [wetland]</t>
   </si>
   <si>
-    <t>Egg in Forest</t>
-  </si>
-  <si>
     <t>[egg] w [forest]</t>
   </si>
   <si>
     <t>Policz liczbę jaj leżących na ptakach &lt;b&gt;w tym konkretnym rzędzie.&lt;/b&gt; Licz wszystkie sztuki, nawet leżące na 1 karcie.&lt;br&gt;&lt;i&gt;Istnieje 1 kopia tego celu dla każdego siedliska.&lt;/i&gt;</t>
   </si>
   <si>
-    <t>Egg in Grassland</t>
-  </si>
-  <si>
     <t>[egg] w [grassland]</t>
   </si>
   <si>
-    <t>Egg in Wetland</t>
-  </si>
-  <si>
     <t>[egg] w [wetland]</t>
   </si>
   <si>
-    <t>Cavity Nest Bird with Egg</t>
-  </si>
-  <si>
     <t>[cavity] [bird] z [egg]</t>
   </si>
   <si>
     <t>Policz liczbę &lt;b&gt;ptaków wijących dany typ gniazda&lt;/b&gt; (liczą się też gniazda z symbolem gwiazdy), na których leży co najmniej 1 jajo. Licz ptaki, a nie jaja.&lt;br&gt;&lt;i&gt;Istnieje 1 kopia tego celu dla każdego typu gniazda.&lt;/i&gt;</t>
   </si>
   <si>
-    <t>Bowl Nest Bird with Egg</t>
-  </si>
-  <si>
     <t>[bowl] [bird] z [egg]</t>
   </si>
   <si>
-    <t>Ground Nest Bird with Egg</t>
-  </si>
-  <si>
     <t>[ground] [bird] z [egg]</t>
   </si>
   <si>
-    <t>Platform Nest Bird with Egg</t>
-  </si>
-  <si>
     <t>[platform] [bird] z [egg]</t>
   </si>
   <si>
-    <t>Egg in Cavity Nest</t>
-  </si>
-  <si>
     <t>[egg] w [cavity]</t>
   </si>
   <si>
     <t>Policz liczbę jaj leżących na ptakach wijących &lt;b&gt;dany typ gniazda&lt;/b&gt; (liczą się też gniazda z symbolem gwiazdy). Licz wszystkie sztuki, nawet leżące na 1 karcie.&lt;br&gt;&lt;i&gt;Istnieje 1 kopia tego celu dla każdego typu gniazda.&lt;/i&gt;</t>
   </si>
   <si>
-    <t>Egg in Bowl Nest</t>
-  </si>
-  <si>
     <t>[egg] w [bowl]</t>
   </si>
   <si>
-    <t>Egg in Ground Nest</t>
-  </si>
-  <si>
     <t>[egg] w [ground]</t>
   </si>
   <si>
-    <t>Egg in Platform Nest</t>
-  </si>
-  <si>
     <t>[egg] w [platform]</t>
   </si>
   <si>
-    <t>Sets of Eggs in 3 Habitats</t>
-  </si>
-  <si>
     <t>zestawy [egg][egg][egg] w [wetland][grassland][forest]</t>
   </si>
   <si>
     <t>1 zestaw jaj składa się z 1 jaja w lesie, 1 jaja na łące i 1 na mokradłach. Policz liczbę takich zestawów.</t>
   </si>
   <si>
-    <t>Total Bird</t>
-  </si>
-  <si>
     <t>wszystkie [bird]</t>
   </si>
   <si>
     <t>Policz liczbę wszystkich zagranych kart ptaków.</t>
   </si>
   <si>
-    <t>Food in Supply</t>
-  </si>
-  <si>
     <t>Żywność w zasobach własnych</t>
   </si>
   <si>
@@ -6388,9 +6352,6 @@
     <t>Policz liczbę wszystkich kart ptaków na ręce.</t>
   </si>
   <si>
-    <t>Birds Worth over 4 Points</t>
-  </si>
-  <si>
     <t>Ptaki warte &gt;4 punkty</t>
   </si>
   <si>
@@ -6400,9 +6361,6 @@
     <t>Policz liczbę zagranych przez siebie kart ptaków, których nadrukowana wartość wynosi więcej niż 4 punkty.</t>
   </si>
   <si>
-    <t>Birds with No Eggs</t>
-  </si>
-  <si>
     <t>Ptaki bez jaj</t>
   </si>
   <si>
@@ -6412,9 +6370,6 @@
     <t>Policz liczbę zagranych przez siebie kart ptaków, na których nie leżą żadne jaja w momencie punktowania tego celu.</t>
   </si>
   <si>
-    <t>Birds in 1 Row</t>
-  </si>
-  <si>
     <t>Ptaki w 1 rzędzie</t>
   </si>
   <si>
@@ -6424,9 +6379,6 @@
     <t>Policz liczbę zagranych przez siebie kart ptaków w rzędzie, w którym masz ich najwięcej.</t>
   </si>
   <si>
-    <t>Filled Columns</t>
-  </si>
-  <si>
     <t>Zapełnione kolumny</t>
   </si>
   <si>
@@ -6436,9 +6388,6 @@
     <t>Policz liczbę kolumn, w których są zapełnione wszystkie 3 pola ptaków.</t>
   </si>
   <si>
-    <t>Brown Powers</t>
-  </si>
-  <si>
     <t>Brązowe zdolności</t>
   </si>
   <si>
@@ -6448,18 +6397,12 @@
     <t>Policz liczbę zagranych przez siebie kart ptaków z brązową zdolnością „GDY AKTYWUJESZ”.</t>
   </si>
   <si>
-    <t>White &amp; No Powers</t>
-  </si>
-  <si>
     <t>Zdolności bez koloru i brak zdolności</t>
   </si>
   <si>
     <t>Policz liczbę zagranych przez siebie kart ptaków, które mają zdolność „GDY ZAGRYWASZ” albo nie mają żadnej zdolności.</t>
   </si>
   <si>
-    <t>Birds with Tucked Cards</t>
-  </si>
-  <si>
     <t>Ptaki z wsuniętymi kartami</t>
   </si>
   <si>
@@ -6469,9 +6412,6 @@
     <t>Policz liczbę zagranych przez siebie kart ptaków, pod którymi znajduje się co najmniej 1 wsunięta karta.</t>
   </si>
   <si>
-    <t>Food Cost of Played Birds</t>
-  </si>
-  <si>
     <t>Koszt w pożywieniu zagranych ptaków</t>
   </si>
   <si>
@@ -6481,9 +6421,6 @@
     <t>Policz koszt w pożywieniu na zagranych przez siebie kartach ptaków, pamiętając, aby policzyć tylko 1 rodzaj pożywienia z kart ptaków, które mają możliwość wyboru rodzaju pożywienia (z ukośnikiem).</t>
   </si>
   <si>
-    <t>Invertebrate in Food Cost of Your Birds</t>
-  </si>
-  <si>
     <t>Bezkręgowiec w koszcie Twoich ptaków</t>
   </si>
   <si>
@@ -6493,27 +6430,18 @@
     <t>Policz liczbę symboli wskazanego rodzaju pożywienia na zagranych przez siebie kartach ptaków. Na przykład, jeśli cel brzmi „[fruit]+[seed] w koszcie Twoich ptaków”, policz wszystkie [fruit] i [seed], które znajdują się w lewym górnym rogu wszystkich zagranych przez Ciebie kart na Twojej planszy. Pamiętaj, aby policzyć tylko 1 rodzaj pożywienia z kart ptaków, które mają możliwość wyboru rodzaju pożywienia np. „[fruit]/[seed]” (te ptaki kosztowały Cię [fruit] ALBO [seed]). Nie licz [wild] ani [nectar].</t>
   </si>
   <si>
-    <t>Fruit + Seed in Food Cost of Your Birds</t>
-  </si>
-  <si>
     <t>Owoc + Ziarno w koszcie Twoich ptaków</t>
   </si>
   <si>
     <t>[fruit] + [seed] w koszcie twoich ptaków</t>
   </si>
   <si>
-    <t>Rodent + Fish in Food Cost of Your Birds</t>
-  </si>
-  <si>
     <t>Gryzoń + Ryba w koszcie Twoich ptaków</t>
   </si>
   <si>
     <t>[rodent] + [fish] w koszcie twoich ptaków</t>
   </si>
   <si>
-    <t>No Goal</t>
-  </si>
-  <si>
     <t>Brak celu</t>
   </si>
   <si>
@@ -6523,9 +6451,6 @@
     <t>Na koniec danej rundy nie punktujecie żadnego celu. Nie odkładajcie w tej rundzie żadnych kostek akcji na planszę celów. We wszystkich kolejnych rundach rozgrywacie o 1 turę więcej.</t>
   </si>
   <si>
-    <t>Beak Pointing Left</t>
-  </si>
-  <si>
     <t>Zwrócone dziobem w lewo</t>
   </si>
   <si>
@@ -6535,18 +6460,12 @@
     <t>Te cele zapewniają punkty za ptaki zwrócone dziobem w określonym kierunku. Do tych celów nie wliczają się ptaki z dziobem skierowanym na wprost albo w górę.&lt;br&gt;Cele związane z kierunkiem dzioba zostały stworzone po to, abyście mieli kolejny powód do przyjrzenia się pięknym ilustracjom. Po przejrzeniu wszystkich kart uznaliśmy, że określenie, w którą stronę skierowany jest dziób ptaka, nie powinno sprawiać trudności. Jeśli jednak uznacie, że jest to kwestia dyskusyjna, usuńcie ten żeton celu z gry. Kilka ptaków wymaga jednak dodatkowych wyjaśnień:&lt;br&gt;&lt;ul&gt;&lt;li&gt;Skrętodziób (dodatek &lt;i&gt;Ptaki Oceanii&lt;/i&gt;) ma dziób skierowany w lewo, chociaż patrzy przed siebie.&lt;/li&gt;&lt;li&gt;Nur lodowiec (gra podstawowa) oraz perkozek zwyczajny (dodatek &lt;i&gt;Ptaki Azji&lt;/i&gt;) mają na kartach ptaki z dziobami skierowanymi w obie strony, więc punktuje oba cele.&lt;/li&gt;&lt;li&gt;Perkoz dwuczuby (dodatek &lt;i&gt;Ptaki Europy&lt;/i&gt;) ma na karcie 2 ptaki z dziobami skierowanymi w tę samą stronę. Na potrzeby celu ta karta liczy się tylko raz.&lt;/li&gt;&lt;/ul&gt;&lt;br&gt;Poniżej prezentujemy listę ptaków, które nie są zwrócone dziobem ani w prawo, ani w lewo.&lt;br&gt;&lt;b&gt;Gra podstawowa&lt;/b&gt;&lt;ul&gt;&lt;li&gt;Górniczek zwyczajny&lt;/li&gt;&lt;li&gt;Kondor kalifornijski&lt;/li&gt;&lt;li&gt;Płomykówka zwyczajna&lt;/li&gt;&lt;li&gt;Pójdźka ziemna&lt;/li&gt;&lt;li&gt;Puchacz wirginijski&lt;/li&gt;&lt;li&gt;Puszczyk kreskowany&lt;/li&gt;&lt;li&gt;Puszczyk plamisty&lt;/li&gt;&lt;li&gt;Syczoń krzykliwy&lt;/li&gt;&lt;/ul&gt;&lt;b&gt;Ptaki Europy&lt;/b&gt;&lt;ul&gt;&lt;li&gt;Pełzacz ogrodowy&lt;/li&gt;&lt;li&gt;Pójdźka zwyczajna&lt;/li&gt;&lt;li&gt;Puchacz śnieżny&lt;/li&gt;&lt;/ul&gt;&lt;b&gt;Ptaki Oceanii&lt;/b&gt;&lt;ul&gt;&lt;li&gt;Kakapo&lt;/li&gt;&lt;li&gt;Sownik australijski&lt;/li&gt;&lt;li&gt;Sowica maskowa&lt;/li&gt;&lt;/ul&gt;&lt;b&gt;Ptaki Azji&lt;/b&gt;&lt;ul&gt;&lt;li&gt;Biegus łyżkodzioby&lt;/li&gt;&lt;li&gt;Gębal cejloński&lt;/li&gt;&lt;li&gt;Pójdźka leśna&lt;/li&gt;&lt;li&gt;Puchacz zwyczajny&lt;/li&gt;&lt;li&gt;Puchówka&lt;/li&gt;&lt;li&gt;Wąsatka&lt;/li&gt;&lt;/ul&gt;</t>
   </si>
   <si>
-    <t>Beak Pointing Right</t>
-  </si>
-  <si>
     <t>Zwrócone dziobem w prawo</t>
   </si>
   <si>
     <t>[beak-right] zwrócone dziobem w prawo</t>
   </si>
   <si>
-    <t>Cubes on "Play a Bird"</t>
-  </si>
-  <si>
     <t>Kostki akcji w rzędzie „zagraj kartę”</t>
   </si>
   <si>
@@ -6556,18 +6475,12 @@
     <t>Policz liczbę kostek, jakie w tej rundzie umieściłeś w rzędzie „Zagraj kartę”. Pamiętaj, że ten cel wymaga zachowania kostek akcji na planszy aż do zakończenia rundy.</t>
   </si>
   <si>
-    <t>Birds Worth Less than or Equal to 3 Points</t>
-  </si>
-  <si>
     <t>Ptaki warte ≤3 punkty</t>
   </si>
   <si>
     <t>[bird] warte ≤3[point]</t>
   </si>
   <si>
-    <t>Pairs of Matching Symbols</t>
-  </si>
-  <si>
     <t>Pary pasujących symboli</t>
   </si>
   <si>
@@ -6577,9 +6490,6 @@
     <t>Policz, ile Twoich znaczników duetu znajduje się na parach pól z identycznymi symbolami. Symbole muszą być takie same, np. 2 gryzonie albo 2 pola rozpiętości skrzydeł &lt;50 cm. Bonusy tych pól nie muszą do siebie pasować. Każdy znacznik liczy się tylko raz. Jeśli masz 4 znaczniki na polach z identycznymi symbolami, liczą się jako 2 pary.</t>
   </si>
   <si>
-    <t>Nest Symbols</t>
-  </si>
-  <si>
     <t>Symbole gniazd</t>
   </si>
   <si>
@@ -6589,9 +6499,6 @@
     <t>Policz wszystkie swoje znaczniki duetu na polach z symbolem gniazda ([bowl], [cavity], [ground], [platform]). Symbole mogą się powtarzać (np.. oba znaczniki na 2 różnych polach [platform] się liczą).</t>
   </si>
   <si>
-    <t>Food Symbols</t>
-  </si>
-  <si>
     <t>Symbole pożywienia</t>
   </si>
   <si>
@@ -6601,9 +6508,6 @@
     <t>Policz wszystkie swoje znaczniki duetu na polach z symbolem pożywienia ([fruit], [seed], [invertebrate], [rodent], [fish]). Symbole mogą się powtarzać (np.. oba znaczniki na 2 różnych polach [fish] się liczą).</t>
   </si>
   <si>
-    <t>Not on Edge of Map</t>
-  </si>
-  <si>
     <t>Nie na skraju mapy</t>
   </si>
   <si>
@@ -6613,18 +6517,12 @@
     <t>Każda krawędź mapy ma 6 pól. Na każdej z bocznych krawędzi znajdują się 3 pola przesunięte do środka, które wciąż są na skraju. Na mapie jest w sumie 20 pól zewnętrznych i 16 pól wewnętrznych. Policz, ile Twoich znaczników znajduje się na skraju mapy (pola zewnętrzne) albo nie na skraju (pola wewnętrzne).</t>
   </si>
   <si>
-    <t>On Edge of Map</t>
-  </si>
-  <si>
     <t>Na skraju mapy</t>
   </si>
   <si>
     <t>[duet-token] na skraju mapy</t>
   </si>
   <si>
-    <t>Tokens in Any One Horizontal Row</t>
-  </si>
-  <si>
     <t>Znaczniki w 1 dowolnym poziomym rzędzie</t>
   </si>
   <si>
@@ -6634,9 +6532,6 @@
     <t>Wybierz najkorzystniejszy dla siebie poziomy rząd i policz, ile Twoich znaczników duetu się w nim znajduje. Znaczniki nie muszą leżeć obok siebie.</t>
   </si>
   <si>
-    <t>Horizontal Rows with at Least One of Your Tokens</t>
-  </si>
-  <si>
     <t>Poziome rzędy z przynajmniej 1 Twoim znacznikiem</t>
   </si>
   <si>
@@ -6646,9 +6541,6 @@
     <t>Policz, w ilu spośród wszystkich 6 poziomych rzędów znajduje się przynajmniej 1 Twój znacznik duetu.</t>
   </si>
   <si>
-    <t>Fewest Tokens on Bonus Spaces</t>
-  </si>
-  <si>
     <t>Najmniej znaczników na polach z bonusami</t>
   </si>
   <si>
@@ -6658,9 +6550,6 @@
     <t>Bonusy na polach mapy zapewniają [dice]/[egg]/[card], gdy umieści się na nich znacznik. Policz, ile Twoich znaczników jest na tych 9 polach. Cel zostaje osiągnięty przez gracza z najmniejszą liczbą takich znaczników.</t>
   </si>
   <si>
-    <t>In Forest</t>
-  </si>
-  <si>
     <t>W lesie</t>
   </si>
   <si>
@@ -6670,27 +6559,18 @@
     <t>Policz, ile Twoich znaczników na mapie znajduje się we wskazanym siedlisku. Ich liczba na mapie może się różnić od liczby ptaków w tym siedlisku na Twojej planszy, jeśli w trakcie gry karty ptaków były przemieszczane.</t>
   </si>
   <si>
-    <t>In Grassland</t>
-  </si>
-  <si>
     <t>Na łące</t>
   </si>
   <si>
     <t>[duet-token] w [grassland]</t>
   </si>
   <si>
-    <t>In Wetland</t>
-  </si>
-  <si>
     <t>Na mokradłach</t>
   </si>
   <si>
     <t>[duet-token] w [wetland]</t>
   </si>
   <si>
-    <t>Total Duet Tokens</t>
-  </si>
-  <si>
     <t>Suma znaczników na mapie</t>
   </si>
   <si>
@@ -6767,6 +6647,141 @@
   </si>
   <si>
     <t>Flavor text</t>
+  </si>
+  <si>
+    <t>Birds in Forest</t>
+  </si>
+  <si>
+    <t>Birds in Grassland</t>
+  </si>
+  <si>
+    <t>Birds in Wetland</t>
+  </si>
+  <si>
+    <t>Eggs in Forest</t>
+  </si>
+  <si>
+    <t>Eggs in Grassland</t>
+  </si>
+  <si>
+    <t>Eggs in Wetland</t>
+  </si>
+  <si>
+    <t>Cavity nest birds with eggs</t>
+  </si>
+  <si>
+    <t>Bowl nest birds with eggs</t>
+  </si>
+  <si>
+    <t>Ground nest birds with eggs</t>
+  </si>
+  <si>
+    <t>Platform nest birds with eggs</t>
+  </si>
+  <si>
+    <t>Eggs in Cavity Nest</t>
+  </si>
+  <si>
+    <t>Eggs in Bowl Nest</t>
+  </si>
+  <si>
+    <t>Eggs in Ground Nest</t>
+  </si>
+  <si>
+    <t>Eggs in Platform Nest</t>
+  </si>
+  <si>
+    <t>Sets of eggs in 3 habitats</t>
+  </si>
+  <si>
+    <t>Total birds</t>
+  </si>
+  <si>
+    <t>Food in personal supply</t>
+  </si>
+  <si>
+    <t>Birds worth over 4 points</t>
+  </si>
+  <si>
+    <t>Birds with no eggs</t>
+  </si>
+  <si>
+    <t>Birds in one row</t>
+  </si>
+  <si>
+    <t>Filled columns</t>
+  </si>
+  <si>
+    <t>Brown powers</t>
+  </si>
+  <si>
+    <t>White &amp; no powers</t>
+  </si>
+  <si>
+    <t>Birds with tucked cards</t>
+  </si>
+  <si>
+    <t>Food cost of played birds</t>
+  </si>
+  <si>
+    <t>Invertebrate in food cost of your birds</t>
+  </si>
+  <si>
+    <t>Fruit + Seed in food cost of your birds</t>
+  </si>
+  <si>
+    <t>Rodent + Fish in food cost of your birds</t>
+  </si>
+  <si>
+    <t>No goal</t>
+  </si>
+  <si>
+    <t>Beak pointing left</t>
+  </si>
+  <si>
+    <t>Beak pointing right</t>
+  </si>
+  <si>
+    <t>Cubes on "play a bird"</t>
+  </si>
+  <si>
+    <t>Birds worth less than or equal to 3 points</t>
+  </si>
+  <si>
+    <t>Duet tokens on pairs of matching symbols</t>
+  </si>
+  <si>
+    <t>Duet tokens on nest symbols</t>
+  </si>
+  <si>
+    <t>Duet tokens on food symbols</t>
+  </si>
+  <si>
+    <t>Duet tokens not on edge of map</t>
+  </si>
+  <si>
+    <t>Duet tokens on edge of map</t>
+  </si>
+  <si>
+    <t>Duet tokens in any one horizontal row</t>
+  </si>
+  <si>
+    <t>Horizontal rows with at least 1 of your duet tokens</t>
+  </si>
+  <si>
+    <t>Fewest duet tokens on bonus spaces</t>
+  </si>
+  <si>
+    <t>Duet tokens in Forest</t>
+  </si>
+  <si>
+    <t>Duet tokens in Grassland</t>
+  </si>
+  <si>
+    <t>Duet tokens in Wetland</t>
+  </si>
+  <si>
+    <t>Total duet tokens</t>
   </si>
 </sst>
 </file>
@@ -6776,7 +6791,7 @@
   <numFmts count="1">
     <numFmt numFmtId="164" formatCode="&quot;PRAWDA&quot;;&quot;PRAWDA&quot;;&quot;FAŁSZ&quot;"/>
   </numFmts>
-  <fonts count="11">
+  <fonts count="12">
     <font>
       <sz val="11"/>
       <color rgb="FF000000"/>
@@ -6788,13 +6803,15 @@
       <sz val="10"/>
       <color rgb="FF000000"/>
       <name val="Calibri"/>
-      <charset val="1"/>
+      <family val="2"/>
+      <charset val="238"/>
     </font>
     <font>
       <sz val="10"/>
       <color rgb="FF000000"/>
       <name val="Arial"/>
-      <charset val="1"/>
+      <family val="2"/>
+      <charset val="238"/>
     </font>
     <font>
       <sz val="9.5"/>
@@ -6805,24 +6822,28 @@
       <sz val="10"/>
       <color rgb="FF000000"/>
       <name val="Times New Roman"/>
-      <charset val="1"/>
-    </font>
-    <font>
-      <sz val="12"/>
-      <color rgb="FF000000"/>
-      <name val="Calibri"/>
+      <family val="1"/>
       <charset val="238"/>
     </font>
     <font>
       <sz val="12"/>
       <color rgb="FF000000"/>
       <name val="Calibri"/>
-      <charset val="1"/>
+      <family val="2"/>
+      <charset val="238"/>
+    </font>
+    <font>
+      <sz val="12"/>
+      <color rgb="FF000000"/>
+      <name val="Calibri"/>
+      <family val="2"/>
+      <charset val="238"/>
     </font>
     <font>
       <sz val="10"/>
       <color rgb="FF000000"/>
       <name val="Calibri"/>
+      <family val="2"/>
       <charset val="238"/>
     </font>
     <font>
@@ -6836,13 +6857,21 @@
       <sz val="12"/>
       <color theme="1"/>
       <name val="Calibri"/>
-      <charset val="1"/>
+      <family val="2"/>
+      <charset val="238"/>
     </font>
     <font>
       <sz val="11"/>
       <name val="Calibri"/>
       <family val="2"/>
       <charset val="1"/>
+    </font>
+    <font>
+      <sz val="11"/>
+      <color theme="1"/>
+      <name val="Calibri"/>
+      <family val="2"/>
+      <charset val="238"/>
     </font>
   </fonts>
   <fills count="2">
@@ -6865,7 +6894,7 @@
   <cellStyleXfs count="1">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
   </cellStyleXfs>
-  <cellXfs count="18">
+  <cellXfs count="20">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyAlignment="1" applyProtection="1"/>
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1" applyProtection="1"/>
@@ -6892,6 +6921,8 @@
     </xf>
     <xf numFmtId="0" fontId="9" fillId="0" borderId="0" xfId="0" applyFont="1"/>
     <xf numFmtId="0" fontId="10" fillId="0" borderId="0" xfId="0" applyFont="1"/>
+    <xf numFmtId="0" fontId="5" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1" applyProtection="1"/>
+    <xf numFmtId="0" fontId="11" fillId="0" borderId="0" xfId="0" applyFont="1"/>
   </cellXfs>
   <cellStyles count="1">
     <cellStyle name="Normal" xfId="0" builtinId="0"/>
@@ -7106,7 +7137,7 @@
         <v>5</v>
       </c>
       <c r="G1" s="17" t="s">
-        <v>2178</v>
+        <v>2133</v>
       </c>
       <c r="H1" s="2" t="s">
         <v>6</v>
@@ -8061,7 +8092,7 @@
         <v>34</v>
       </c>
       <c r="B34" s="15" t="s">
-        <v>2171</v>
+        <v>2126</v>
       </c>
       <c r="C34" s="1" t="s">
         <v>154</v>
@@ -10201,7 +10232,7 @@
         <v>106</v>
       </c>
       <c r="B106" s="1" t="s">
-        <v>2172</v>
+        <v>2127</v>
       </c>
       <c r="C106" s="1" t="s">
         <v>425</v>
@@ -11167,7 +11198,7 @@
         <v>139</v>
       </c>
       <c r="B139" s="1" t="s">
-        <v>2174</v>
+        <v>2129</v>
       </c>
       <c r="C139" s="1" t="s">
         <v>552</v>
@@ -12326,7 +12357,7 @@
         <v>696</v>
       </c>
       <c r="C179" s="1" t="s">
-        <v>2175</v>
+        <v>2130</v>
       </c>
       <c r="D179" s="3" t="s">
         <v>13</v>
@@ -15851,7 +15882,7 @@
         <v>298</v>
       </c>
       <c r="B298" s="16" t="s">
-        <v>2177</v>
+        <v>2132</v>
       </c>
       <c r="C298" s="3" t="s">
         <v>1122</v>
@@ -16255,7 +16286,7 @@
         <v>312</v>
       </c>
       <c r="B312" s="3" t="s">
-        <v>2173</v>
+        <v>2128</v>
       </c>
       <c r="C312" s="3" t="s">
         <v>1180</v>
@@ -18739,7 +18770,7 @@
         <v>1562</v>
       </c>
       <c r="C399" s="3" t="s">
-        <v>2176</v>
+        <v>2131</v>
       </c>
       <c r="D399" s="3" t="s">
         <v>1375</v>
@@ -21424,643 +21455,643 @@
       <c r="A2" s="1">
         <v>2000</v>
       </c>
-      <c r="B2" s="9" t="s">
-        <v>2006</v>
+      <c r="B2" s="18" t="s">
+        <v>2134</v>
       </c>
       <c r="C2" s="9" t="s">
         <v>13</v>
       </c>
       <c r="D2" s="2"/>
       <c r="E2" s="9" t="s">
+        <v>2006</v>
+      </c>
+      <c r="F2" s="9" t="s">
         <v>2007</v>
-      </c>
-      <c r="F2" s="9" t="s">
-        <v>2008</v>
       </c>
     </row>
     <row r="3" spans="1:6" ht="15.75">
       <c r="A3" s="1">
         <v>2001</v>
       </c>
-      <c r="B3" s="9" t="s">
-        <v>2009</v>
+      <c r="B3" s="18" t="s">
+        <v>2135</v>
       </c>
       <c r="C3" s="9" t="s">
         <v>13</v>
       </c>
       <c r="D3" s="2"/>
       <c r="E3" s="9" t="s">
-        <v>2010</v>
+        <v>2008</v>
       </c>
       <c r="F3" s="9" t="s">
-        <v>2008</v>
+        <v>2007</v>
       </c>
     </row>
     <row r="4" spans="1:6" ht="15.75">
       <c r="A4" s="1">
         <v>2002</v>
       </c>
-      <c r="B4" s="9" t="s">
-        <v>2011</v>
+      <c r="B4" s="18" t="s">
+        <v>2136</v>
       </c>
       <c r="C4" s="9" t="s">
         <v>13</v>
       </c>
       <c r="D4" s="2"/>
       <c r="E4" s="9" t="s">
-        <v>2012</v>
+        <v>2009</v>
       </c>
       <c r="F4" s="9" t="s">
-        <v>2008</v>
+        <v>2007</v>
       </c>
     </row>
     <row r="5" spans="1:6" ht="15.75">
       <c r="A5" s="2">
         <v>2013</v>
       </c>
-      <c r="B5" s="9" t="s">
-        <v>2013</v>
+      <c r="B5" s="18" t="s">
+        <v>2137</v>
       </c>
       <c r="C5" s="9" t="s">
         <v>13</v>
       </c>
       <c r="D5" s="2"/>
       <c r="E5" s="9" t="s">
-        <v>2014</v>
+        <v>2010</v>
       </c>
       <c r="F5" s="9" t="s">
-        <v>2015</v>
+        <v>2011</v>
       </c>
     </row>
     <row r="6" spans="1:6" ht="15.75">
       <c r="A6" s="2">
         <v>2014</v>
       </c>
-      <c r="B6" s="9" t="s">
-        <v>2016</v>
+      <c r="B6" s="18" t="s">
+        <v>2138</v>
       </c>
       <c r="C6" s="9" t="s">
         <v>13</v>
       </c>
       <c r="D6" s="2"/>
       <c r="E6" s="9" t="s">
-        <v>2017</v>
+        <v>2012</v>
       </c>
       <c r="F6" s="9" t="s">
-        <v>2015</v>
+        <v>2011</v>
       </c>
     </row>
     <row r="7" spans="1:6" ht="15.75">
       <c r="A7" s="2">
         <v>2017</v>
       </c>
-      <c r="B7" s="9" t="s">
-        <v>2018</v>
+      <c r="B7" s="18" t="s">
+        <v>2139</v>
       </c>
       <c r="C7" s="9" t="s">
         <v>13</v>
       </c>
       <c r="D7" s="2"/>
       <c r="E7" s="9" t="s">
-        <v>2019</v>
+        <v>2013</v>
       </c>
       <c r="F7" s="9" t="s">
-        <v>2015</v>
+        <v>2011</v>
       </c>
     </row>
     <row r="8" spans="1:6" ht="15.75">
       <c r="A8" s="2">
         <v>2010</v>
       </c>
-      <c r="B8" s="9" t="s">
-        <v>2020</v>
+      <c r="B8" s="18" t="s">
+        <v>2140</v>
       </c>
       <c r="C8" s="9" t="s">
         <v>13</v>
       </c>
       <c r="D8" s="2"/>
       <c r="E8" s="9" t="s">
-        <v>2021</v>
+        <v>2014</v>
       </c>
       <c r="F8" s="9" t="s">
-        <v>2022</v>
+        <v>2015</v>
       </c>
     </row>
     <row r="9" spans="1:6" ht="15.75">
       <c r="A9" s="2">
         <v>2008</v>
       </c>
-      <c r="B9" s="9" t="s">
-        <v>2023</v>
+      <c r="B9" s="18" t="s">
+        <v>2141</v>
       </c>
       <c r="C9" s="9" t="s">
         <v>13</v>
       </c>
       <c r="D9" s="2"/>
       <c r="E9" s="9" t="s">
-        <v>2024</v>
+        <v>2016</v>
       </c>
       <c r="F9" s="9" t="s">
-        <v>2022</v>
+        <v>2015</v>
       </c>
     </row>
     <row r="10" spans="1:6" ht="15.75">
       <c r="A10" s="2">
         <v>2021</v>
       </c>
-      <c r="B10" s="9" t="s">
-        <v>2025</v>
+      <c r="B10" s="18" t="s">
+        <v>2142</v>
       </c>
       <c r="C10" s="9" t="s">
         <v>13</v>
       </c>
       <c r="D10" s="2"/>
       <c r="E10" s="9" t="s">
-        <v>2026</v>
+        <v>2017</v>
       </c>
       <c r="F10" s="9" t="s">
-        <v>2022</v>
+        <v>2015</v>
       </c>
     </row>
     <row r="11" spans="1:6" ht="15.75">
       <c r="A11" s="2">
         <v>2022</v>
       </c>
-      <c r="B11" s="9" t="s">
-        <v>2027</v>
+      <c r="B11" s="18" t="s">
+        <v>2143</v>
       </c>
       <c r="C11" s="9" t="s">
         <v>13</v>
       </c>
       <c r="D11" s="2"/>
       <c r="E11" s="9" t="s">
-        <v>2028</v>
+        <v>2018</v>
       </c>
       <c r="F11" s="9" t="s">
-        <v>2022</v>
+        <v>2015</v>
       </c>
     </row>
     <row r="12" spans="1:6" ht="15.75">
       <c r="A12" s="2">
         <v>2012</v>
       </c>
-      <c r="B12" s="9" t="s">
-        <v>2029</v>
+      <c r="B12" s="18" t="s">
+        <v>2144</v>
       </c>
       <c r="C12" s="9" t="s">
         <v>13</v>
       </c>
       <c r="D12" s="2"/>
       <c r="E12" s="9" t="s">
-        <v>2030</v>
+        <v>2019</v>
       </c>
       <c r="F12" s="9" t="s">
-        <v>2031</v>
+        <v>2020</v>
       </c>
     </row>
     <row r="13" spans="1:6" ht="15.75">
       <c r="A13" s="2">
         <v>2011</v>
       </c>
-      <c r="B13" s="9" t="s">
-        <v>2032</v>
+      <c r="B13" s="18" t="s">
+        <v>2145</v>
       </c>
       <c r="C13" s="9" t="s">
         <v>13</v>
       </c>
       <c r="D13" s="2"/>
       <c r="E13" s="9" t="s">
-        <v>2033</v>
+        <v>2021</v>
       </c>
       <c r="F13" s="9" t="s">
-        <v>2031</v>
+        <v>2020</v>
       </c>
     </row>
     <row r="14" spans="1:6" ht="15.75">
       <c r="A14" s="2">
         <v>2015</v>
       </c>
-      <c r="B14" s="9" t="s">
-        <v>2034</v>
+      <c r="B14" s="18" t="s">
+        <v>2146</v>
       </c>
       <c r="C14" s="9" t="s">
         <v>13</v>
       </c>
       <c r="D14" s="2"/>
       <c r="E14" s="9" t="s">
-        <v>2035</v>
+        <v>2022</v>
       </c>
       <c r="F14" s="9" t="s">
-        <v>2031</v>
+        <v>2020</v>
       </c>
     </row>
     <row r="15" spans="1:6" ht="15.75">
       <c r="A15" s="2">
         <v>2016</v>
       </c>
-      <c r="B15" s="9" t="s">
-        <v>2036</v>
+      <c r="B15" s="18" t="s">
+        <v>2147</v>
       </c>
       <c r="C15" s="9" t="s">
         <v>13</v>
       </c>
       <c r="D15" s="2"/>
       <c r="E15" s="9" t="s">
-        <v>2037</v>
+        <v>2023</v>
       </c>
       <c r="F15" s="9" t="s">
-        <v>2031</v>
+        <v>2020</v>
       </c>
     </row>
     <row r="16" spans="1:6" ht="15.75">
       <c r="A16" s="2">
         <v>2023</v>
       </c>
-      <c r="B16" s="9" t="s">
-        <v>2038</v>
+      <c r="B16" s="18" t="s">
+        <v>2148</v>
       </c>
       <c r="C16" s="9" t="s">
         <v>13</v>
       </c>
       <c r="D16" s="2"/>
       <c r="E16" s="9" t="s">
-        <v>2039</v>
+        <v>2024</v>
       </c>
       <c r="F16" s="9" t="s">
-        <v>2040</v>
+        <v>2025</v>
       </c>
     </row>
     <row r="17" spans="1:6" ht="15.75">
       <c r="A17" s="2">
         <v>2024</v>
       </c>
-      <c r="B17" s="9" t="s">
-        <v>2041</v>
+      <c r="B17" s="18" t="s">
+        <v>2149</v>
       </c>
       <c r="C17" s="9" t="s">
         <v>13</v>
       </c>
       <c r="D17" s="2"/>
       <c r="E17" s="9" t="s">
-        <v>2042</v>
+        <v>2026</v>
       </c>
       <c r="F17" s="9" t="s">
-        <v>2043</v>
+        <v>2027</v>
       </c>
     </row>
     <row r="18" spans="1:6" ht="15.75">
       <c r="A18" s="2">
         <v>2020</v>
       </c>
-      <c r="B18" s="9" t="s">
-        <v>2044</v>
+      <c r="B18" s="18" t="s">
+        <v>2150</v>
       </c>
       <c r="C18" s="9" t="s">
         <v>89</v>
       </c>
       <c r="D18" s="2" t="s">
-        <v>2045</v>
+        <v>2028</v>
       </c>
       <c r="E18" s="9" t="s">
-        <v>2046</v>
+        <v>2029</v>
       </c>
       <c r="F18" s="9" t="s">
-        <v>2047</v>
+        <v>2030</v>
       </c>
     </row>
     <row r="19" spans="1:6" ht="15.75">
       <c r="A19" s="1">
         <v>2003</v>
       </c>
-      <c r="B19" s="9" t="s">
-        <v>2048</v>
+      <c r="B19" s="18" t="s">
+        <v>2031</v>
       </c>
       <c r="C19" s="9" t="s">
         <v>89</v>
       </c>
       <c r="D19" s="2" t="s">
-        <v>2049</v>
+        <v>2032</v>
       </c>
       <c r="E19" s="9" t="s">
-        <v>2050</v>
+        <v>2033</v>
       </c>
       <c r="F19" s="9" t="s">
-        <v>2051</v>
+        <v>2034</v>
       </c>
     </row>
     <row r="20" spans="1:6" ht="15.75">
       <c r="A20" s="2">
         <v>2004</v>
       </c>
-      <c r="B20" s="9" t="s">
-        <v>2052</v>
+      <c r="B20" s="18" t="s">
+        <v>2151</v>
       </c>
       <c r="C20" s="9" t="s">
         <v>89</v>
       </c>
       <c r="D20" s="2" t="s">
-        <v>2053</v>
+        <v>2035</v>
       </c>
       <c r="E20" s="9" t="s">
-        <v>2054</v>
+        <v>2036</v>
       </c>
       <c r="F20" s="9" t="s">
-        <v>2055</v>
+        <v>2037</v>
       </c>
     </row>
     <row r="21" spans="1:6" ht="15.75">
       <c r="A21" s="2">
         <v>2006</v>
       </c>
-      <c r="B21" s="9" t="s">
-        <v>2056</v>
+      <c r="B21" s="18" t="s">
+        <v>2152</v>
       </c>
       <c r="C21" s="9" t="s">
         <v>89</v>
       </c>
       <c r="D21" s="2" t="s">
-        <v>2057</v>
+        <v>2038</v>
       </c>
       <c r="E21" s="9" t="s">
-        <v>2058</v>
+        <v>2039</v>
       </c>
       <c r="F21" s="9" t="s">
-        <v>2059</v>
+        <v>2040</v>
       </c>
     </row>
     <row r="22" spans="1:6" ht="15.75">
       <c r="A22" s="2">
         <v>2005</v>
       </c>
-      <c r="B22" s="9" t="s">
-        <v>2060</v>
+      <c r="B22" s="18" t="s">
+        <v>2153</v>
       </c>
       <c r="C22" s="9" t="s">
         <v>89</v>
       </c>
       <c r="D22" s="2" t="s">
-        <v>2061</v>
+        <v>2041</v>
       </c>
       <c r="E22" s="9" t="s">
-        <v>2062</v>
+        <v>2042</v>
       </c>
       <c r="F22" s="9" t="s">
-        <v>2063</v>
+        <v>2043</v>
       </c>
     </row>
     <row r="23" spans="1:6" ht="15.75">
       <c r="A23" s="2">
         <v>2018</v>
       </c>
-      <c r="B23" s="9" t="s">
-        <v>2064</v>
+      <c r="B23" s="18" t="s">
+        <v>2154</v>
       </c>
       <c r="C23" s="9" t="s">
         <v>89</v>
       </c>
       <c r="D23" s="2" t="s">
-        <v>2065</v>
+        <v>2044</v>
       </c>
       <c r="E23" s="9" t="s">
-        <v>2066</v>
+        <v>2045</v>
       </c>
       <c r="F23" s="9" t="s">
-        <v>2067</v>
+        <v>2046</v>
       </c>
     </row>
     <row r="24" spans="1:6" ht="15.75">
       <c r="A24" s="2">
         <v>2009</v>
       </c>
-      <c r="B24" s="9" t="s">
-        <v>2068</v>
+      <c r="B24" s="18" t="s">
+        <v>2155</v>
       </c>
       <c r="C24" s="9" t="s">
         <v>89</v>
       </c>
       <c r="D24" s="2" t="s">
-        <v>2069</v>
+        <v>2047</v>
       </c>
       <c r="E24" s="9" t="s">
-        <v>2070</v>
+        <v>2048</v>
       </c>
       <c r="F24" s="9" t="s">
-        <v>2071</v>
+        <v>2049</v>
       </c>
     </row>
     <row r="25" spans="1:6" ht="15.75">
       <c r="A25" s="2">
         <v>2025</v>
       </c>
-      <c r="B25" s="9" t="s">
-        <v>2072</v>
+      <c r="B25" s="18" t="s">
+        <v>2156</v>
       </c>
       <c r="C25" s="9" t="s">
         <v>89</v>
       </c>
       <c r="D25" s="2" t="s">
-        <v>2073</v>
+        <v>2050</v>
       </c>
       <c r="E25" s="9"/>
       <c r="F25" s="9" t="s">
-        <v>2074</v>
+        <v>2051</v>
       </c>
     </row>
     <row r="26" spans="1:6" ht="15.75">
       <c r="A26" s="2">
         <v>2007</v>
       </c>
-      <c r="B26" s="9" t="s">
-        <v>2075</v>
+      <c r="B26" s="18" t="s">
+        <v>2157</v>
       </c>
       <c r="C26" s="9" t="s">
         <v>89</v>
       </c>
       <c r="D26" s="2" t="s">
-        <v>2076</v>
+        <v>2052</v>
       </c>
       <c r="E26" s="9" t="s">
-        <v>2077</v>
+        <v>2053</v>
       </c>
       <c r="F26" s="9" t="s">
-        <v>2078</v>
+        <v>2054</v>
       </c>
     </row>
     <row r="27" spans="1:6" ht="15.75">
       <c r="A27" s="2">
         <v>2019</v>
       </c>
-      <c r="B27" s="9" t="s">
-        <v>2079</v>
+      <c r="B27" s="18" t="s">
+        <v>2158</v>
       </c>
       <c r="C27" s="9" t="s">
         <v>89</v>
       </c>
       <c r="D27" s="2" t="s">
-        <v>2080</v>
+        <v>2055</v>
       </c>
       <c r="E27" s="2" t="s">
-        <v>2081</v>
+        <v>2056</v>
       </c>
       <c r="F27" s="9" t="s">
-        <v>2082</v>
+        <v>2057</v>
       </c>
     </row>
     <row r="28" spans="1:6" ht="15.75">
       <c r="A28" s="2">
         <v>2031</v>
       </c>
-      <c r="B28" s="9" t="s">
-        <v>2083</v>
+      <c r="B28" s="18" t="s">
+        <v>2159</v>
       </c>
       <c r="C28" s="9" t="s">
         <v>974</v>
       </c>
       <c r="D28" s="2" t="s">
-        <v>2084</v>
+        <v>2058</v>
       </c>
       <c r="E28" s="9" t="s">
-        <v>2085</v>
+        <v>2059</v>
       </c>
       <c r="F28" s="9" t="s">
-        <v>2086</v>
+        <v>2060</v>
       </c>
     </row>
     <row r="29" spans="1:6" ht="15.75">
       <c r="A29" s="2">
         <v>2030</v>
       </c>
-      <c r="B29" s="9" t="s">
-        <v>2087</v>
+      <c r="B29" s="18" t="s">
+        <v>2160</v>
       </c>
       <c r="C29" s="9" t="s">
         <v>974</v>
       </c>
       <c r="D29" s="2" t="s">
-        <v>2088</v>
+        <v>2061</v>
       </c>
       <c r="E29" s="9" t="s">
-        <v>2089</v>
+        <v>2062</v>
       </c>
       <c r="F29" s="9" t="s">
-        <v>2086</v>
+        <v>2060</v>
       </c>
     </row>
     <row r="30" spans="1:6" ht="15.75">
       <c r="A30" s="2">
         <v>2033</v>
       </c>
-      <c r="B30" s="9" t="s">
-        <v>2090</v>
+      <c r="B30" s="18" t="s">
+        <v>2161</v>
       </c>
       <c r="C30" s="9" t="s">
         <v>974</v>
       </c>
       <c r="D30" s="2" t="s">
-        <v>2091</v>
+        <v>2063</v>
       </c>
       <c r="E30" s="9" t="s">
-        <v>2092</v>
+        <v>2064</v>
       </c>
       <c r="F30" s="9" t="s">
-        <v>2086</v>
+        <v>2060</v>
       </c>
     </row>
     <row r="31" spans="1:6" ht="15.75">
       <c r="A31" s="2">
         <v>2032</v>
       </c>
-      <c r="B31" s="9" t="s">
-        <v>2093</v>
+      <c r="B31" s="18" t="s">
+        <v>2162</v>
       </c>
       <c r="C31" s="9" t="s">
         <v>974</v>
       </c>
       <c r="D31" s="2" t="s">
-        <v>2094</v>
+        <v>2065</v>
       </c>
       <c r="E31" s="2" t="s">
-        <v>2095</v>
+        <v>2066</v>
       </c>
       <c r="F31" s="9" t="s">
-        <v>2096</v>
+        <v>2067</v>
       </c>
     </row>
     <row r="32" spans="1:6" ht="15.75">
       <c r="A32" s="2">
         <v>2026</v>
       </c>
-      <c r="B32" s="9" t="s">
-        <v>2097</v>
+      <c r="B32" s="18" t="s">
+        <v>2163</v>
       </c>
       <c r="C32" s="9" t="s">
         <v>974</v>
       </c>
       <c r="D32" s="2" t="s">
-        <v>2098</v>
+        <v>2068</v>
       </c>
       <c r="E32" s="9" t="s">
-        <v>2099</v>
+        <v>2069</v>
       </c>
       <c r="F32" s="9" t="s">
-        <v>2100</v>
+        <v>2070</v>
       </c>
     </row>
     <row r="33" spans="1:6" ht="15.75">
       <c r="A33" s="2">
         <v>2027</v>
       </c>
-      <c r="B33" s="9" t="s">
-        <v>2101</v>
+      <c r="B33" s="18" t="s">
+        <v>2164</v>
       </c>
       <c r="C33" s="9" t="s">
         <v>974</v>
       </c>
       <c r="D33" s="2" t="s">
-        <v>2102</v>
+        <v>2071</v>
       </c>
       <c r="E33" s="9" t="s">
-        <v>2103</v>
+        <v>2072</v>
       </c>
       <c r="F33" s="9" t="s">
-        <v>2100</v>
+        <v>2070</v>
       </c>
     </row>
     <row r="34" spans="1:6" ht="15.75">
       <c r="A34" s="2">
         <v>2029</v>
       </c>
-      <c r="B34" s="9" t="s">
-        <v>2104</v>
+      <c r="B34" s="18" t="s">
+        <v>2165</v>
       </c>
       <c r="C34" s="9" t="s">
         <v>974</v>
       </c>
       <c r="D34" s="2" t="s">
-        <v>2105</v>
+        <v>2073</v>
       </c>
       <c r="E34" s="9" t="s">
-        <v>2106</v>
+        <v>2074</v>
       </c>
       <c r="F34" s="9" t="s">
-        <v>2107</v>
+        <v>2075</v>
       </c>
     </row>
     <row r="35" spans="1:6" ht="15.75">
       <c r="A35" s="2">
         <v>2028</v>
       </c>
-      <c r="B35" s="9" t="s">
-        <v>2108</v>
+      <c r="B35" s="18" t="s">
+        <v>2166</v>
       </c>
       <c r="C35" s="9" t="s">
         <v>974</v>
       </c>
       <c r="D35" s="2" t="s">
-        <v>2109</v>
+        <v>2076</v>
       </c>
       <c r="E35" s="9" t="s">
-        <v>2110</v>
+        <v>2077</v>
       </c>
       <c r="F35" s="9"/>
     </row>
@@ -22068,240 +22099,240 @@
       <c r="A36" s="2">
         <v>2043</v>
       </c>
-      <c r="B36" s="9" t="s">
-        <v>2111</v>
+      <c r="B36" s="19" t="s">
+        <v>2167</v>
       </c>
       <c r="C36" s="9" t="s">
         <v>1375</v>
       </c>
       <c r="D36" s="9" t="s">
-        <v>2112</v>
+        <v>2078</v>
       </c>
       <c r="E36" s="9" t="s">
-        <v>2113</v>
+        <v>2079</v>
       </c>
       <c r="F36" s="9" t="s">
-        <v>2114</v>
+        <v>2080</v>
       </c>
     </row>
     <row r="37" spans="1:6" ht="15.75">
       <c r="A37" s="2">
         <v>2040</v>
       </c>
-      <c r="B37" s="9" t="s">
-        <v>2115</v>
+      <c r="B37" s="18" t="s">
+        <v>2168</v>
       </c>
       <c r="C37" s="9" t="s">
         <v>1375</v>
       </c>
       <c r="D37" s="9" t="s">
-        <v>2116</v>
+        <v>2081</v>
       </c>
       <c r="E37" s="9" t="s">
-        <v>2117</v>
+        <v>2082</v>
       </c>
       <c r="F37" s="9" t="s">
-        <v>2118</v>
+        <v>2083</v>
       </c>
     </row>
     <row r="38" spans="1:6" ht="15.75">
       <c r="A38" s="2">
         <v>2035</v>
       </c>
-      <c r="B38" s="9" t="s">
-        <v>2119</v>
+      <c r="B38" s="18" t="s">
+        <v>2169</v>
       </c>
       <c r="C38" s="9" t="s">
         <v>1375</v>
       </c>
       <c r="D38" s="9" t="s">
-        <v>2120</v>
+        <v>2084</v>
       </c>
       <c r="E38" s="9" t="s">
-        <v>2121</v>
+        <v>2085</v>
       </c>
       <c r="F38" s="9" t="s">
-        <v>2122</v>
+        <v>2086</v>
       </c>
     </row>
     <row r="39" spans="1:6" ht="15.75">
       <c r="A39" s="2">
         <v>2041</v>
       </c>
-      <c r="B39" s="9" t="s">
-        <v>2123</v>
+      <c r="B39" s="18" t="s">
+        <v>2170</v>
       </c>
       <c r="C39" s="9" t="s">
         <v>1375</v>
       </c>
       <c r="D39" s="9" t="s">
-        <v>2124</v>
+        <v>2087</v>
       </c>
       <c r="E39" s="9" t="s">
-        <v>2125</v>
+        <v>2088</v>
       </c>
       <c r="F39" s="9" t="s">
-        <v>2126</v>
+        <v>2089</v>
       </c>
     </row>
     <row r="40" spans="1:6" ht="15.75">
       <c r="A40" s="2">
         <v>2042</v>
       </c>
-      <c r="B40" s="9" t="s">
-        <v>2127</v>
+      <c r="B40" s="18" t="s">
+        <v>2171</v>
       </c>
       <c r="C40" s="9" t="s">
         <v>1375</v>
       </c>
       <c r="D40" s="9" t="s">
-        <v>2128</v>
+        <v>2090</v>
       </c>
       <c r="E40" s="9" t="s">
-        <v>2129</v>
+        <v>2091</v>
       </c>
       <c r="F40" s="9" t="s">
-        <v>2126</v>
+        <v>2089</v>
       </c>
     </row>
     <row r="41" spans="1:6" ht="15.75">
       <c r="A41" s="2">
         <v>2044</v>
       </c>
-      <c r="B41" s="9" t="s">
-        <v>2130</v>
+      <c r="B41" s="18" t="s">
+        <v>2172</v>
       </c>
       <c r="C41" s="9" t="s">
         <v>1375</v>
       </c>
       <c r="D41" s="9" t="s">
-        <v>2131</v>
+        <v>2092</v>
       </c>
       <c r="E41" s="9" t="s">
-        <v>2132</v>
+        <v>2093</v>
       </c>
       <c r="F41" s="9" t="s">
-        <v>2133</v>
+        <v>2094</v>
       </c>
     </row>
     <row r="42" spans="1:6" ht="15.75">
       <c r="A42" s="2">
         <v>2036</v>
       </c>
-      <c r="B42" s="9" t="s">
-        <v>2134</v>
+      <c r="B42" s="18" t="s">
+        <v>2173</v>
       </c>
       <c r="C42" s="9" t="s">
         <v>1375</v>
       </c>
       <c r="D42" s="9" t="s">
-        <v>2135</v>
+        <v>2095</v>
       </c>
       <c r="E42" s="9" t="s">
-        <v>2136</v>
+        <v>2096</v>
       </c>
       <c r="F42" s="9" t="s">
-        <v>2137</v>
+        <v>2097</v>
       </c>
     </row>
     <row r="43" spans="1:6" ht="15.75">
       <c r="A43" s="2">
         <v>2034</v>
       </c>
-      <c r="B43" s="9" t="s">
-        <v>2138</v>
+      <c r="B43" s="18" t="s">
+        <v>2174</v>
       </c>
       <c r="C43" s="9" t="s">
         <v>1375</v>
       </c>
       <c r="D43" s="9" t="s">
-        <v>2139</v>
+        <v>2098</v>
       </c>
       <c r="E43" s="9" t="s">
-        <v>2140</v>
+        <v>2099</v>
       </c>
       <c r="F43" s="9" t="s">
-        <v>2141</v>
+        <v>2100</v>
       </c>
     </row>
     <row r="44" spans="1:6" ht="15.75">
       <c r="A44" s="2">
         <v>2037</v>
       </c>
-      <c r="B44" s="9" t="s">
-        <v>2142</v>
+      <c r="B44" s="18" t="s">
+        <v>2175</v>
       </c>
       <c r="C44" s="9" t="s">
         <v>1375</v>
       </c>
       <c r="D44" s="9" t="s">
-        <v>2143</v>
+        <v>2101</v>
       </c>
       <c r="E44" s="9" t="s">
-        <v>2144</v>
+        <v>2102</v>
       </c>
       <c r="F44" s="9" t="s">
-        <v>2145</v>
+        <v>2103</v>
       </c>
     </row>
     <row r="45" spans="1:6" ht="15.75">
       <c r="A45" s="2">
         <v>2038</v>
       </c>
-      <c r="B45" s="9" t="s">
-        <v>2146</v>
+      <c r="B45" s="18" t="s">
+        <v>2176</v>
       </c>
       <c r="C45" s="9" t="s">
         <v>1375</v>
       </c>
       <c r="D45" s="9" t="s">
-        <v>2147</v>
+        <v>2104</v>
       </c>
       <c r="E45" s="9" t="s">
-        <v>2148</v>
+        <v>2105</v>
       </c>
       <c r="F45" s="9" t="s">
-        <v>2145</v>
+        <v>2103</v>
       </c>
     </row>
     <row r="46" spans="1:6" ht="15.75">
       <c r="A46" s="2">
         <v>2039</v>
       </c>
-      <c r="B46" s="9" t="s">
-        <v>2149</v>
+      <c r="B46" s="18" t="s">
+        <v>2177</v>
       </c>
       <c r="C46" s="9" t="s">
         <v>1375</v>
       </c>
       <c r="D46" s="9" t="s">
-        <v>2150</v>
+        <v>2106</v>
       </c>
       <c r="E46" s="9" t="s">
-        <v>2151</v>
+        <v>2107</v>
       </c>
       <c r="F46" s="9" t="s">
-        <v>2145</v>
+        <v>2103</v>
       </c>
     </row>
     <row r="47" spans="1:6" ht="15.75">
       <c r="A47" s="2">
         <v>2045</v>
       </c>
-      <c r="B47" s="9" t="s">
-        <v>2152</v>
+      <c r="B47" s="18" t="s">
+        <v>2178</v>
       </c>
       <c r="C47" s="9" t="s">
         <v>1375</v>
       </c>
       <c r="D47" s="9" t="s">
-        <v>2153</v>
+        <v>2108</v>
       </c>
       <c r="E47" s="9" t="s">
-        <v>2154</v>
+        <v>2109</v>
       </c>
       <c r="F47" s="9" t="s">
-        <v>2155</v>
+        <v>2110</v>
       </c>
     </row>
   </sheetData>
@@ -22329,55 +22360,55 @@
         <v>1</v>
       </c>
       <c r="B1" s="2" t="s">
-        <v>2156</v>
+        <v>2111</v>
       </c>
     </row>
     <row r="2" spans="1:2">
       <c r="A2" s="1" t="s">
-        <v>2157</v>
+        <v>2112</v>
       </c>
       <c r="B2" s="4" t="s">
-        <v>2158</v>
+        <v>2113</v>
       </c>
     </row>
     <row r="3" spans="1:2">
       <c r="A3" s="1" t="s">
-        <v>2159</v>
+        <v>2114</v>
       </c>
       <c r="B3" s="4" t="s">
-        <v>2160</v>
+        <v>2115</v>
       </c>
     </row>
     <row r="4" spans="1:2">
       <c r="A4" s="1" t="s">
-        <v>2161</v>
+        <v>2116</v>
       </c>
       <c r="B4" s="4" t="s">
-        <v>2162</v>
+        <v>2117</v>
       </c>
     </row>
     <row r="5" spans="1:2">
       <c r="A5" s="1" t="s">
-        <v>2163</v>
+        <v>2118</v>
       </c>
       <c r="B5" s="4" t="s">
-        <v>2164</v>
+        <v>2119</v>
       </c>
     </row>
     <row r="6" spans="1:2">
       <c r="A6" s="1" t="s">
-        <v>2165</v>
+        <v>2120</v>
       </c>
       <c r="B6" s="4" t="s">
-        <v>2166</v>
+        <v>2121</v>
       </c>
     </row>
     <row r="7" spans="1:2">
       <c r="A7" s="1" t="s">
-        <v>2167</v>
+        <v>2122</v>
       </c>
       <c r="B7" s="4" t="s">
-        <v>2168</v>
+        <v>2123</v>
       </c>
     </row>
   </sheetData>
@@ -22403,12 +22434,12 @@
         <v>1778</v>
       </c>
       <c r="B1" s="13" t="s">
-        <v>2169</v>
+        <v>2124</v>
       </c>
     </row>
     <row r="2" spans="1:2">
       <c r="A2" s="1" t="s">
-        <v>2170</v>
+        <v>2125</v>
       </c>
       <c r="B2" s="14" t="b">
         <f>FALSE()</f>
